--- a/03_Prompting/outputs/GPT/RESULT_clap_gpt-4o_zeroshot_cot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_clap_gpt-4o_zeroshot_cot.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8160,7 +8160,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8585,7 +8585,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -9673,7 +9673,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9758,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9996,7 +9996,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -10183,7 +10183,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -10489,7 +10489,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11356,7 +11356,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11407,7 +11407,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -12053,7 +12053,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12206,7 +12206,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12223,7 +12223,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12546,7 +12546,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12580,7 +12580,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12682,7 +12682,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12869,7 +12869,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12886,7 +12886,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12937,7 +12937,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13090,7 +13090,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13192,7 +13192,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13345,7 +13345,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -13498,7 +13498,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13719,7 +13719,7 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -13753,7 +13753,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13787,7 +13787,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14093,7 +14093,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -14348,7 +14348,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14654,7 +14654,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -14671,7 +14671,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -14977,7 +14977,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15045,7 +15045,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15181,7 +15181,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15334,7 +15334,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15640,7 +15640,7 @@
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -15776,7 +15776,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15793,7 +15793,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -16167,7 +16167,7 @@
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -16184,7 +16184,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -16235,7 +16235,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -16711,7 +16711,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -16762,7 +16762,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16813,7 +16813,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16915,7 +16915,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -17068,7 +17068,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17442,7 +17442,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17476,7 +17476,7 @@
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17561,7 +17561,7 @@
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18071,7 +18071,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -18258,7 +18258,7 @@
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18445,7 +18445,7 @@
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18479,7 +18479,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18513,7 +18513,7 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18547,7 +18547,7 @@
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18700,7 +18700,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18751,7 +18751,7 @@
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18802,7 +18802,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18870,7 +18870,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18989,7 +18989,7 @@
       </c>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19006,7 +19006,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19040,7 +19040,7 @@
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19057,7 +19057,7 @@
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19193,7 +19193,7 @@
       </c>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19448,7 +19448,7 @@
       </c>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19465,7 +19465,7 @@
       </c>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19482,7 +19482,7 @@
       </c>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19516,7 +19516,7 @@
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19567,7 +19567,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19839,7 +19839,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19890,7 +19890,7 @@
       </c>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19924,7 +19924,7 @@
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20162,7 +20162,7 @@
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20213,7 +20213,7 @@
       </c>
       <c r="C1164" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20383,7 +20383,7 @@
       </c>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20417,7 +20417,7 @@
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20825,7 +20825,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20876,7 +20876,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20893,7 +20893,7 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -21267,7 +21267,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21318,7 +21318,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21505,7 +21505,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21692,7 +21692,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21726,7 +21726,7 @@
       </c>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21794,7 +21794,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21811,7 +21811,7 @@
       </c>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21862,7 +21862,7 @@
       </c>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21998,7 +21998,7 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22032,7 +22032,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22100,7 +22100,7 @@
       </c>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22117,7 +22117,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="C1282" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22270,7 +22270,7 @@
       </c>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22287,7 +22287,7 @@
       </c>
       <c r="C1286" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22304,7 +22304,7 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22321,7 +22321,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22372,7 +22372,7 @@
       </c>
       <c r="C1291" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="C1293" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22440,7 +22440,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="C1298" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22678,7 +22678,7 @@
       </c>
       <c r="C1309" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22814,7 +22814,7 @@
       </c>
       <c r="C1317" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22882,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C1325" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22967,7 +22967,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -23086,7 +23086,7 @@
       </c>
       <c r="C1333" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23137,7 +23137,7 @@
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23154,7 +23154,7 @@
       </c>
       <c r="C1337" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -23171,7 +23171,7 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="C1344" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="C1347" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -23341,7 +23341,7 @@
       </c>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23375,7 +23375,7 @@
       </c>
       <c r="C1350" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23392,7 +23392,7 @@
       </c>
       <c r="C1351" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -23426,7 +23426,7 @@
       </c>
       <c r="C1353" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23460,7 +23460,7 @@
       </c>
       <c r="C1355" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -23528,7 +23528,7 @@
       </c>
       <c r="C1359" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="C1367" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23851,7 +23851,7 @@
       </c>
       <c r="C1378" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -24004,7 +24004,7 @@
       </c>
       <c r="C1387" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -24021,7 +24021,7 @@
       </c>
       <c r="C1388" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -24157,7 +24157,7 @@
       </c>
       <c r="C1396" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24395,7 +24395,7 @@
       </c>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -24412,7 +24412,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -24514,7 +24514,7 @@
       </c>
       <c r="C1417" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24548,7 +24548,7 @@
       </c>
       <c r="C1419" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24582,7 +24582,7 @@
       </c>
       <c r="C1421" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -24701,7 +24701,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -24786,7 +24786,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -24803,7 +24803,7 @@
       </c>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24905,7 +24905,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24922,7 +24922,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="C1443" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -24973,7 +24973,7 @@
       </c>
       <c r="C1444" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -24990,7 +24990,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25007,7 +25007,7 @@
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25126,7 +25126,7 @@
       </c>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25364,7 +25364,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25483,7 +25483,7 @@
       </c>
       <c r="C1474" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25602,7 +25602,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25653,7 +25653,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -25857,7 +25857,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25874,7 +25874,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25891,7 +25891,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25908,7 +25908,7 @@
       </c>
       <c r="C1499" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25976,7 +25976,7 @@
       </c>
       <c r="C1503" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25993,7 +25993,7 @@
       </c>
       <c r="C1504" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26027,7 +26027,7 @@
       </c>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -26044,7 +26044,7 @@
       </c>
       <c r="C1507" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -26112,7 +26112,7 @@
       </c>
       <c r="C1511" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -26180,7 +26180,7 @@
       </c>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -26350,7 +26350,7 @@
       </c>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26452,7 +26452,7 @@
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -26503,7 +26503,7 @@
       </c>
       <c r="C1534" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -26911,7 +26911,7 @@
       </c>
       <c r="C1558" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -27098,7 +27098,7 @@
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27115,7 +27115,7 @@
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27217,7 +27217,7 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -27285,7 +27285,7 @@
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -27404,7 +27404,7 @@
       </c>
       <c r="C1587" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -27506,7 +27506,7 @@
       </c>
       <c r="C1593" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="C1607" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -27761,7 +27761,7 @@
       </c>
       <c r="C1608" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="C1610" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -27829,7 +27829,7 @@
       </c>
       <c r="C1612" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="C1613" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -28220,7 +28220,7 @@
       </c>
       <c r="C1635" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28322,7 +28322,7 @@
       </c>
       <c r="C1641" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28390,7 +28390,7 @@
       </c>
       <c r="C1645" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -28509,7 +28509,7 @@
       </c>
       <c r="C1652" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -28866,7 +28866,7 @@
       </c>
       <c r="C1673" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -28951,7 +28951,7 @@
       </c>
       <c r="C1678" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29155,7 +29155,7 @@
       </c>
       <c r="C1690" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -29172,7 +29172,7 @@
       </c>
       <c r="C1691" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="C1693" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29223,7 +29223,7 @@
       </c>
       <c r="C1694" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -29240,7 +29240,7 @@
       </c>
       <c r="C1695" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29478,7 +29478,7 @@
       </c>
       <c r="C1709" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29546,7 +29546,7 @@
       </c>
       <c r="C1713" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29597,7 +29597,7 @@
       </c>
       <c r="C1716" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29614,7 +29614,7 @@
       </c>
       <c r="C1717" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -29699,7 +29699,7 @@
       </c>
       <c r="C1722" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29835,7 +29835,7 @@
       </c>
       <c r="C1730" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -29903,7 +29903,7 @@
       </c>
       <c r="C1734" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29920,7 +29920,7 @@
       </c>
       <c r="C1735" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="C1737" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -30158,7 +30158,7 @@
       </c>
       <c r="C1749" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30804,7 +30804,7 @@
       </c>
       <c r="C1787" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -30889,7 +30889,7 @@
       </c>
       <c r="C1792" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -30940,7 +30940,7 @@
       </c>
       <c r="C1795" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -31229,7 +31229,7 @@
       </c>
       <c r="C1812" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="C1815" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="C1821" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -31433,7 +31433,7 @@
       </c>
       <c r="C1824" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -31450,7 +31450,7 @@
       </c>
       <c r="C1825" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -31739,7 +31739,7 @@
       </c>
       <c r="C1842" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="C1843" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -32045,7 +32045,7 @@
       </c>
       <c r="C1860" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -32147,7 +32147,7 @@
       </c>
       <c r="C1866" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="C1867" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="C1873" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="C1876" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32453,7 +32453,7 @@
       </c>
       <c r="C1884" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32504,7 +32504,7 @@
       </c>
       <c r="C1887" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -32572,7 +32572,7 @@
       </c>
       <c r="C1891" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -32640,7 +32640,7 @@
       </c>
       <c r="C1895" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -32895,7 +32895,7 @@
       </c>
       <c r="C1910" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33167,7 +33167,7 @@
       </c>
       <c r="C1926" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33218,7 +33218,7 @@
       </c>
       <c r="C1929" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="C1930" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="C1935" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="C1940" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -33490,7 +33490,7 @@
       </c>
       <c r="C1945" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -33575,7 +33575,7 @@
       </c>
       <c r="C1950" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33643,7 +33643,7 @@
       </c>
       <c r="C1954" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33694,7 +33694,7 @@
       </c>
       <c r="C1957" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33779,7 +33779,7 @@
       </c>
       <c r="C1962" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="C1965" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33847,7 +33847,7 @@
       </c>
       <c r="C1966" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33932,7 +33932,7 @@
       </c>
       <c r="C1971" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="C1973" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34221,7 +34221,7 @@
       </c>
       <c r="C1988" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34272,7 +34272,7 @@
       </c>
       <c r="C1991" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34289,7 +34289,7 @@
       </c>
       <c r="C1992" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34340,7 +34340,7 @@
       </c>
       <c r="C1995" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34374,7 +34374,7 @@
       </c>
       <c r="C1997" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34459,7 +34459,7 @@
       </c>
       <c r="C2002" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34629,7 +34629,7 @@
       </c>
       <c r="C2012" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34918,7 +34918,7 @@
       </c>
       <c r="C2029" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35020,7 +35020,7 @@
       </c>
       <c r="C2035" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35105,7 +35105,7 @@
       </c>
       <c r="C2040" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35615,7 +35615,7 @@
       </c>
       <c r="C2070" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35717,7 +35717,7 @@
       </c>
       <c r="C2076" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36040,7 +36040,7 @@
       </c>
       <c r="C2095" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36193,7 +36193,7 @@
       </c>
       <c r="C2104" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36244,7 +36244,7 @@
       </c>
       <c r="C2107" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36397,7 +36397,7 @@
       </c>
       <c r="C2116" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="C2119" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36499,7 +36499,7 @@
       </c>
       <c r="C2122" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36584,7 +36584,7 @@
       </c>
       <c r="C2127" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36635,7 +36635,7 @@
       </c>
       <c r="C2130" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36703,7 +36703,7 @@
       </c>
       <c r="C2134" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -36839,7 +36839,7 @@
       </c>
       <c r="C2142" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36992,7 +36992,7 @@
       </c>
       <c r="C2151" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37043,7 +37043,7 @@
       </c>
       <c r="C2154" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37111,7 +37111,7 @@
       </c>
       <c r="C2158" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -37145,7 +37145,7 @@
       </c>
       <c r="C2160" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37298,7 +37298,7 @@
       </c>
       <c r="C2169" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="C2170" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37502,7 +37502,7 @@
       </c>
       <c r="C2181" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C2196" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37808,7 +37808,7 @@
       </c>
       <c r="C2199" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37876,7 +37876,7 @@
       </c>
       <c r="C2203" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38012,7 +38012,7 @@
       </c>
       <c r="C2211" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38063,7 +38063,7 @@
       </c>
       <c r="C2214" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38284,7 +38284,7 @@
       </c>
       <c r="C2227" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38335,7 +38335,7 @@
       </c>
       <c r="C2230" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38488,7 +38488,7 @@
       </c>
       <c r="C2239" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38777,7 +38777,7 @@
       </c>
       <c r="C2256" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38913,7 +38913,7 @@
       </c>
       <c r="C2264" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -38947,7 +38947,7 @@
       </c>
       <c r="C2266" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39049,7 +39049,7 @@
       </c>
       <c r="C2272" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39066,7 +39066,7 @@
       </c>
       <c r="C2273" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39117,7 +39117,7 @@
       </c>
       <c r="C2276" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39134,7 +39134,7 @@
       </c>
       <c r="C2277" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39440,7 +39440,7 @@
       </c>
       <c r="C2295" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39491,7 +39491,7 @@
       </c>
       <c r="C2298" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39593,7 +39593,7 @@
       </c>
       <c r="C2304" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39661,7 +39661,7 @@
       </c>
       <c r="C2308" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39712,7 +39712,7 @@
       </c>
       <c r="C2311" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39746,7 +39746,7 @@
       </c>
       <c r="C2313" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39814,7 +39814,7 @@
       </c>
       <c r="C2317" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39984,7 +39984,7 @@
       </c>
       <c r="C2327" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40018,7 +40018,7 @@
       </c>
       <c r="C2329" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40120,7 +40120,7 @@
       </c>
       <c r="C2335" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40205,7 +40205,7 @@
       </c>
       <c r="C2340" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40222,7 +40222,7 @@
       </c>
       <c r="C2341" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40239,7 +40239,7 @@
       </c>
       <c r="C2342" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40273,7 +40273,7 @@
       </c>
       <c r="C2344" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40324,7 +40324,7 @@
       </c>
       <c r="C2347" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40375,7 +40375,7 @@
       </c>
       <c r="C2350" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40392,7 +40392,7 @@
       </c>
       <c r="C2351" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40426,7 +40426,7 @@
       </c>
       <c r="C2353" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40443,7 +40443,7 @@
       </c>
       <c r="C2354" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40460,7 +40460,7 @@
       </c>
       <c r="C2355" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40562,7 +40562,7 @@
       </c>
       <c r="C2361" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40579,7 +40579,7 @@
       </c>
       <c r="C2362" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40783,7 +40783,7 @@
       </c>
       <c r="C2374" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40851,7 +40851,7 @@
       </c>
       <c r="C2378" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -41123,7 +41123,7 @@
       </c>
       <c r="C2394" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41140,7 +41140,7 @@
       </c>
       <c r="C2395" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41191,7 +41191,7 @@
       </c>
       <c r="C2398" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -41208,7 +41208,7 @@
       </c>
       <c r="C2399" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41327,7 +41327,7 @@
       </c>
       <c r="C2406" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41412,7 +41412,7 @@
       </c>
       <c r="C2411" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41599,7 +41599,7 @@
       </c>
       <c r="C2422" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41735,7 +41735,7 @@
       </c>
       <c r="C2430" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42347,7 +42347,7 @@
       </c>
       <c r="C2466" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42568,7 +42568,7 @@
       </c>
       <c r="C2479" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="C2481" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -42942,7 +42942,7 @@
       </c>
       <c r="C2501" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42959,7 +42959,7 @@
       </c>
       <c r="C2502" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42976,7 +42976,7 @@
       </c>
       <c r="C2503" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -43129,7 +43129,7 @@
       </c>
       <c r="C2512" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43197,7 +43197,7 @@
       </c>
       <c r="C2516" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43214,7 +43214,7 @@
       </c>
       <c r="C2517" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43282,7 +43282,7 @@
       </c>
       <c r="C2521" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43333,7 +43333,7 @@
       </c>
       <c r="C2524" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43418,7 +43418,7 @@
       </c>
       <c r="C2529" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43469,7 +43469,7 @@
       </c>
       <c r="C2532" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43520,7 +43520,7 @@
       </c>
       <c r="C2535" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="C2538" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43622,7 +43622,7 @@
       </c>
       <c r="C2541" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43877,7 +43877,7 @@
       </c>
       <c r="C2556" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -44336,7 +44336,7 @@
       </c>
       <c r="C2583" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44540,7 +44540,7 @@
       </c>
       <c r="C2595" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44846,7 +44846,7 @@
       </c>
       <c r="C2613" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45050,7 +45050,7 @@
       </c>
       <c r="C2625" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45067,7 +45067,7 @@
       </c>
       <c r="C2626" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -45101,7 +45101,7 @@
       </c>
       <c r="C2628" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -45373,7 +45373,7 @@
       </c>
       <c r="C2644" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45390,7 +45390,7 @@
       </c>
       <c r="C2645" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45713,7 +45713,7 @@
       </c>
       <c r="C2664" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45917,7 +45917,7 @@
       </c>
       <c r="C2676" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -45985,7 +45985,7 @@
       </c>
       <c r="C2680" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46019,7 +46019,7 @@
       </c>
       <c r="C2682" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46104,7 +46104,7 @@
       </c>
       <c r="C2687" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -46206,7 +46206,7 @@
       </c>
       <c r="C2693" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46342,7 +46342,7 @@
       </c>
       <c r="C2701" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46359,7 +46359,7 @@
       </c>
       <c r="C2702" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46512,7 +46512,7 @@
       </c>
       <c r="C2711" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46682,7 +46682,7 @@
       </c>
       <c r="C2721" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46784,7 +46784,7 @@
       </c>
       <c r="C2727" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47090,7 +47090,7 @@
       </c>
       <c r="C2745" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47345,7 +47345,7 @@
       </c>
       <c r="C2760" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47515,7 +47515,7 @@
       </c>
       <c r="C2770" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47532,7 +47532,7 @@
       </c>
       <c r="C2771" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47549,7 +47549,7 @@
       </c>
       <c r="C2772" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -47685,7 +47685,7 @@
       </c>
       <c r="C2780" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47753,7 +47753,7 @@
       </c>
       <c r="C2784" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -47923,7 +47923,7 @@
       </c>
       <c r="C2794" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48161,7 +48161,7 @@
       </c>
       <c r="C2808" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48195,7 +48195,7 @@
       </c>
       <c r="C2810" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48314,7 +48314,7 @@
       </c>
       <c r="C2817" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48331,7 +48331,7 @@
       </c>
       <c r="C2818" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -48535,7 +48535,7 @@
       </c>
       <c r="C2830" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -48552,7 +48552,7 @@
       </c>
       <c r="C2831" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48705,7 +48705,7 @@
       </c>
       <c r="C2840" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48824,7 +48824,7 @@
       </c>
       <c r="C2847" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -48875,7 +48875,7 @@
       </c>
       <c r="C2850" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49045,7 +49045,7 @@
       </c>
       <c r="C2860" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49130,7 +49130,7 @@
       </c>
       <c r="C2865" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49249,7 +49249,7 @@
       </c>
       <c r="C2872" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -49283,7 +49283,7 @@
       </c>
       <c r="C2874" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -49368,7 +49368,7 @@
       </c>
       <c r="C2879" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -49912,7 +49912,7 @@
       </c>
       <c r="C2911" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -50048,7 +50048,7 @@
       </c>
       <c r="C2919" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50133,7 +50133,7 @@
       </c>
       <c r="C2924" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -50167,7 +50167,7 @@
       </c>
       <c r="C2926" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -50218,7 +50218,7 @@
       </c>
       <c r="C2929" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50252,7 +50252,7 @@
       </c>
       <c r="C2931" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50286,7 +50286,7 @@
       </c>
       <c r="C2933" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -50405,7 +50405,7 @@
       </c>
       <c r="C2940" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50915,7 +50915,7 @@
       </c>
       <c r="C2970" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -50966,7 +50966,7 @@
       </c>
       <c r="C2973" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50983,7 +50983,7 @@
       </c>
       <c r="C2974" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -51017,7 +51017,7 @@
       </c>
       <c r="C2976" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -51051,7 +51051,7 @@
       </c>
       <c r="C2978" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -51170,7 +51170,7 @@
       </c>
       <c r="C2985" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -51479,7 +51479,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.543</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="3">
@@ -51489,7 +51489,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5846076330464024</v>
+        <v>0.6104833585029593</v>
       </c>
     </row>
     <row r="4">
@@ -51499,7 +51499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5893615535558506</v>
+        <v>0.620847051759718</v>
       </c>
     </row>
     <row r="5">
@@ -51509,7 +51509,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6064829159797006</v>
+        <v>0.628004987448996</v>
       </c>
     </row>
     <row r="6">
@@ -51519,7 +51519,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.718141184262164</v>
+        <v>0.7319162268571958</v>
       </c>
     </row>
     <row r="7">
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>742.5987195100006</v>
+        <v>1703.838033142994</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2475329065033335</v>
+        <v>0.5679460110476648</v>
       </c>
     </row>
   </sheetData>
